--- a/artfynd/A 56141-2025 artfynd.xlsx
+++ b/artfynd/A 56141-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126051180</v>
       </c>
       <c r="B2" t="n">
-        <v>91245</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,11 +775,11 @@
         <v>126051265</v>
       </c>
       <c r="B3" t="n">
-        <v>91699</v>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -792,12 +792,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -872,11 +872,11 @@
         <v>126051072</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -969,7 +969,7 @@
         <v>126051096</v>
       </c>
       <c r="B5" t="n">
-        <v>80111</v>
+        <v>80460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126051394</v>
+        <v>126051445</v>
       </c>
       <c r="B6" t="n">
-        <v>57761</v>
+        <v>80461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,43 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599720</v>
+        <v>599724</v>
       </c>
       <c r="R6" t="n">
-        <v>7054210</v>
+        <v>7054250</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1169,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126051445</v>
+        <v>126051454</v>
       </c>
       <c r="B7" t="n">
-        <v>80112</v>
+        <v>80461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1204,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599724</v>
+        <v>599726</v>
       </c>
       <c r="R7" t="n">
-        <v>7054250</v>
+        <v>7054252</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1266,45 +1257,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126051454</v>
+        <v>126051394</v>
       </c>
       <c r="B8" t="n">
-        <v>80112</v>
+        <v>58057</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599726</v>
+        <v>599720</v>
       </c>
       <c r="R8" t="n">
-        <v>7054252</v>
+        <v>7054210</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 56141-2025 artfynd.xlsx
+++ b/artfynd/A 56141-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126051180</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126051265</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126051072</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126051096</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126051445</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126051454</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,8 +1395,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126051394</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>